--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_175_Mayotte_France.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_175_Mayotte_France.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R57a09c411c3e4540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd9ce0f778fae4579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R459f2b281dfa4041"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2fcdf17497544fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9ad910946edd4242"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9a15c33b80bb43e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2633b7f99d674a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9f0ce8f9c8f64e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1ffa91d4ac36489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R551cd9d5cacb45ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R18b9e170b4bf48a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8a056377bf984d34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ175CommercialTable" displayName="EEZ175CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ175CommercialTable" displayName="EEZ175CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ175FunctionalTable" displayName="EEZ175FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ175FunctionalTable" displayName="EEZ175FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ175ValidationTable" displayName="EEZ175ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ175ValidationTable" displayName="EEZ175ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7662,7 +7616,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b20ccfef7374562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5437fd7aabc6476d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7672,20 +7626,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7693,606 +7637,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6.8355996107</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6.8355996107</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$105,A2,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1083.3695289388272</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1083.3695289388272</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.12237250930000002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.17</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>147.91083881682073</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.12237250930000002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>147.91083881682073</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$105,A3,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>18.100220498682198</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.17</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>147.91083881682073</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>18.100220498682198</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.10543927789999999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.10543927789999999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>316.2277660168379</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$105,A4,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>33.34282730074555</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>33.34282730074555</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>12.7381198897</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3235023832360127</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>210.62134570243248</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>12.7381198897</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>370.986793812878</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$105,A5,'Species'!$U$2:$U$105))</x:f>
-        <x:v>4725.674257083854</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3235023832360127</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>210.62134570243248</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2682.9199528875347</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2042.7543041963195</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.7613921921143316</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.7613921921143316</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4.840103997</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4.840103997</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$105,A6,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>60.933299175498206</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>60.933299175498206</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>150.2241701022</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.354026691243236</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>225.95746368321707</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>150.2241701022</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>234.87807180727563</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$105,A7,'Species'!$U$2:$U$105))</x:f>
-        <x:v>35284.36341245292</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.354026691243236</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>225.95746368321707</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>33944.27246020928</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1340.0909522436414</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0394791478831824</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.039479147883182505</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1572.6467617203</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.927583855835971</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>846.4159834279274</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1572.6467617203</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1262.9176158888</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$105,A8,'Species'!$U$2:$U$105))</x:f>
-        <x:v>1986123.2989470428</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.927583855835971</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>846.4159834279274</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1331113.355406233</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>655009.9435408097</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4920767573103584</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.49207675731035827</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.07249220640000001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>398.1071705534973</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.07249220640000001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$105,A9,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>28.859667177084134</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>28.859667177084134</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13.852317241000002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.174484760000379</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1494.461598702618</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13.852317241000002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1551.8147003374802</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$105,A10,'Species'!$U$2:$U$105))</x:f>
-        <x:v>21496.22952832213</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.174484760000379</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1494.461598702618</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>20701.7561697207</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>794.4733586014299</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0383770996087502</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03837709960875019</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>912.8002530722001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.411655499035915</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2580.212643579201</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>912.8002530722001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2597.670987477106</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$105,A11,'Species'!$U$2:$U$105))</x:f>
-        <x:v>2371154.734767414</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.411655499035915</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2580.212643579201</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2355218.754039185</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>15935.980728229042</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0067662422867936</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0067662422867935034</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R989acb1234174f9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81d3fc0fd3940c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8302,20 +7852,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8323,984 +7863,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14.217364470400002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.616855143907783</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>413.86161095449603</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14.217364470400002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>420.3691171758658</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$105,A2,'Species'!$U$2:$U$105))</x:f>
-        <x:v>5976.54095098957</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.616855143907783</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>413.86161095449603</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>5884.0213632469595</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>92.51958774261038</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0157238701274116</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.015723870127411572</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1.4194264925</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1.4194264925</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$105,A3,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3733.4720700710795</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>3733.4720700710795</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2.2603069087</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.112687118323013</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1296.2450720057407</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2.2603069087</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1517.3229312095461</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$105,A4,'Species'!$U$2:$U$105))</x:f>
-        <x:v>3429.615504141872</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.112687118323013</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1296.2450720057407</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2929.9116916229045</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>499.7038125189674</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1705525166330788</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.1705525166330788</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1100.6507819115</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.401410163327282</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2520.0558355791027</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1100.6507819115</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2550.8864580609857</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$105,A5,'Species'!$U$2:$U$105))</x:f>
-        <x:v>2807635.1746322806</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.401410163327282</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2520.0558355791027</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2773701.4258907777</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>33933.74874150287</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0122341029300244</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.012234102930024275</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>105.91804543900001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.376937521507977</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2381.976768660901</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>105.91804543900001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2460.137947632487</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$105,A6,'Species'!$U$2:$U$105))</x:f>
-        <x:v>260573.00292354595</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.376937521507977</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2381.976768660901</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>252294.32361766775</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>8278.679305878206</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0328135773614309</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03281357736143083</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>13.852317241000002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.174484760000379</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1494.461598702618</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>13.852317241000002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1551.8147003374802</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$105,A7,'Species'!$U$2:$U$105))</x:f>
-        <x:v>21496.22952832213</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.174484760000379</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1494.461598702618</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>20701.7561697207</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>794.4733586014299</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0383770996087502</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.03837709960875019</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.12237250930000002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.17</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>147.91083881682073</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.12237250930000002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>147.91083881682073</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$105,A8,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>18.100220498682198</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.17</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>147.91083881682073</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>18.100220498682198</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>14.9611677543</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>14.9611677543</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$105,A9,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3054.6783900520522</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>3054.6783900520522</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>84.6922400265</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5063063899464555</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>320.8532110090418</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>84.6922400265</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>410.444966347534</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$105,A10,'Species'!$U$2:$U$105))</x:f>
-        <x:v>34761.503607574065</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5063063899464555</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>320.8532110090418</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>27173.77716005102</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7587.726447523044</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.279229729559937</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.2792297295599372</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>461.7743436717</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.063430731438876</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1157.2594382450202</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>461.7743436717</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1322.3634703020357</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$105,A11,'Species'!$U$2:$U$105))</x:f>
-        <x:v>610633.5235941542</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.063430731438876</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1157.2594382450202</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>534392.7175534745</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>76240.80604067969</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1426681231542992</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.14266812315429914</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>717.4850210377999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.6892720060674513</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>488.9585065419288</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>717.4850210377999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>858.1504647776229</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$105,A12,'Species'!$U$2:$U$105))</x:f>
-        <x:v>615710.1042745706</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.6892720060674513</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>488.9585065419288</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>350820.404352847</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>264889.6999217236</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.755057849073407</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.755057849073407</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>4.840103997</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>4.840103997</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$105,A13,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>60.933299175498206</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>60.933299175498206</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1.2764816442</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.263869989642582</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>183.59886396771958</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1.2764816442</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>183.9776971705242</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$105,A14,'Species'!$U$2:$U$105))</x:f>
-        <x:v>234.8441533803604</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.263869989642582</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>183.59886396771958</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>234.36057975076682</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0.48357362959359307</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0020633744382603</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0020633744382602846</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>91.3554607102</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.621483721607513</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>418.29600962604593</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>91.3554607102</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>418.47088403824563</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$105,A15,'Species'!$U$2:$U$105))</x:f>
-        <x:v>38229.60040511861</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.621483721607513</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>418.29600962604593</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>38213.62467262568</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>15.975732492930547</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.000418063783004</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.00041806378300393885</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>17.5711108851</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.175560995899233</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>149.81696535728497</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>17.5711108851</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>149.96906238320267</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$105,A16,'Species'!$U$2:$U$105))</x:f>
-        <x:v>2635.1230244697335</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.175560995899233</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>149.81696535728497</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2632.45051076204</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2.6725137076937244</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0010152189743997</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.0010152189743996695</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>41.7356456496</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.266116620149722</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>184.5510923670095</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>41.7356456496</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>282.56702073746317</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$105,A17,'Species'!$U$2:$U$105))</x:f>
-        <x:v>11793.117049761939</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.266116620149722</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>184.5510923670095</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>7702.358995276108</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>4090.758054485831</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.5311045690021345</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5311045690021345</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>0.10543927789999999</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>0.10543927789999999</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>316.2277660168379</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$105,A18,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>33.34282730074555</x:v>
       </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>33.34282730074555</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6031ea096b8d480d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcab9b1d87914ca5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9475,7 +8376,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9574,7 +8475,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4420008.906455407</x:v>
+        <x:v>3744885.6635713265</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9588,7 +8489,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4420008.906455407</x:v>
+        <x:v>4023581.6593649206</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9602,7 +8503,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-675123.2428840804</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9616,7 +8517,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-396427.24709048634</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9627,9 +8528,9 @@
         <x:v>EEZ_175</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9641,47 +8542,19 @@
         <x:v>EEZ_175</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_175</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_175</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65055b4ce13d449d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ea85ce56aa49fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9728,7 +8601,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
